--- a/模型分析/PSO_運行時間分析.xlsx
+++ b/模型分析/PSO_運行時間分析.xlsx
@@ -413,28 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>類別類型</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>資料集名稱</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>運行時間(秒)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>多類別</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Abalone_3class</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>3775.993765592575</v>
       </c>
     </row>
